--- a/resources/tool_kii_wash_service_provider_iphra_v2.xlsx
+++ b/resources/tool_kii_wash_service_provider_iphra_v2.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\saeed.rahman\Desktop\public_health_resources\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\R Projects\SaeedR1987\public_health_resources\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7188438E-0AC1-448E-B15B-A5D3BC4729C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95FA4A0C-2831-422F-8E0E-DA3B5D5D3EB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="17385" xr2:uid="{27C29DD6-0256-4DF1-82F8-B613F9F4F125}"/>
+    <workbookView xWindow="1170" yWindow="720" windowWidth="14535" windowHeight="15480" activeTab="1" xr2:uid="{27C29DD6-0256-4DF1-82F8-B613F9F4F125}"/>
   </bookViews>
   <sheets>
     <sheet name="survey" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="180">
   <si>
     <t>type</t>
   </si>
@@ -528,19 +528,58 @@
     <t>vector_control</t>
   </si>
   <si>
-    <t>42003, 57007, 20201</t>
-  </si>
-  <si>
-    <t>43404, 57201, 20202</t>
-  </si>
-  <si>
-    <t>43403, 57202, 20301</t>
-  </si>
-  <si>
     <t>Among the community, you’re reaching through your programs what are the main water, sanitation, or hygiene needs you observe?</t>
   </si>
   <si>
     <t xml:space="preserve">Do you have any new programs or assistance delivery planned in the next 3 months? </t>
+  </si>
+  <si>
+    <t>13408, 13412, 15002</t>
+  </si>
+  <si>
+    <t>13303, 13409, 15001</t>
+  </si>
+  <si>
+    <t>13303, 13308</t>
+  </si>
+  <si>
+    <t>enum_id</t>
+  </si>
+  <si>
+    <t>Team 1</t>
+  </si>
+  <si>
+    <t>Équipe 1</t>
+  </si>
+  <si>
+    <t>Team 2</t>
+  </si>
+  <si>
+    <t>Équipe 2</t>
+  </si>
+  <si>
+    <t>Team 3</t>
+  </si>
+  <si>
+    <t>Équipe 3</t>
+  </si>
+  <si>
+    <t>Team 4</t>
+  </si>
+  <si>
+    <t>Équipe 4</t>
+  </si>
+  <si>
+    <t>Team 5</t>
+  </si>
+  <si>
+    <t>Équipe 5</t>
+  </si>
+  <si>
+    <t>Homme</t>
+  </si>
+  <si>
+    <t>Femme</t>
   </si>
 </sst>
 </file>
@@ -593,7 +632,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -618,6 +657,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -631,7 +676,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -649,11 +694,22 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="6">
+  <dxfs count="7">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1323,8 +1379,8 @@
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>162</v>
+      <c r="A16" s="11" t="s">
+        <v>166</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>140</v>
@@ -1337,8 +1393,8 @@
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>163</v>
+      <c r="A17" s="11" t="s">
+        <v>165</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>19</v>
@@ -1354,7 +1410,7 @@
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
+      <c r="A18" s="11" t="s">
         <v>164</v>
       </c>
       <c r="B18" s="2" t="s">
@@ -1368,7 +1424,7 @@
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
+      <c r="A19" s="11" t="s">
         <v>164</v>
       </c>
       <c r="B19" s="2" t="s">
@@ -1383,7 +1439,7 @@
       <c r="J19" s="4"/>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
+      <c r="A20" s="11" t="s">
         <v>164</v>
       </c>
       <c r="B20" s="5" t="s">
@@ -1398,8 +1454,8 @@
       <c r="J20" s="4"/>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A21">
-        <v>42201</v>
+      <c r="A21" s="11">
+        <v>13305</v>
       </c>
       <c r="B21" s="5" t="s">
         <v>19</v>
@@ -1408,12 +1464,12 @@
         <v>133</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A22">
-        <v>43501</v>
+      <c r="A22" s="11">
+        <v>13305</v>
       </c>
       <c r="B22" s="5" t="s">
         <v>19</v>
@@ -1426,8 +1482,8 @@
       </c>
     </row>
     <row r="23" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A23">
-        <v>43501</v>
+      <c r="A23" s="11">
+        <v>13410</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>111</v>
@@ -1440,8 +1496,8 @@
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A24">
-        <v>43501</v>
+      <c r="A24" s="11">
+        <v>13410</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>19</v>
@@ -1454,8 +1510,8 @@
       </c>
     </row>
     <row r="25" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A25">
-        <v>43501</v>
+      <c r="A25" s="11">
+        <v>13410</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>19</v>
@@ -1468,8 +1524,8 @@
       </c>
     </row>
     <row r="26" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A26">
-        <v>43502</v>
+      <c r="A26" s="11">
+        <v>13411</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>96</v>
@@ -1482,8 +1538,8 @@
       </c>
     </row>
     <row r="27" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A27">
-        <v>43502</v>
+      <c r="A27" s="11">
+        <v>13411</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>19</v>
@@ -1496,8 +1552,8 @@
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A28">
-        <v>43502</v>
+      <c r="A28" s="11">
+        <v>13411</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>111</v>
@@ -1510,8 +1566,8 @@
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A29">
-        <v>43502</v>
+      <c r="A29" s="11">
+        <v>13411</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>19</v>
@@ -1524,8 +1580,8 @@
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A30">
-        <v>43502</v>
+      <c r="A30" s="11">
+        <v>13411</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>19</v>
@@ -1538,8 +1594,8 @@
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A31">
-        <v>42301</v>
+      <c r="A31" s="11">
+        <v>13306</v>
       </c>
       <c r="B31" s="3" t="s">
         <v>111</v>
@@ -1548,12 +1604,12 @@
         <v>126</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A32">
-        <v>42301</v>
+      <c r="A32" s="11">
+        <v>13306</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>19</v>
@@ -1566,8 +1622,8 @@
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A33">
-        <v>42301</v>
+      <c r="A33" s="11">
+        <v>13306</v>
       </c>
       <c r="B33" s="3" t="s">
         <v>19</v>
@@ -1636,10 +1692,10 @@
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
   <conditionalFormatting sqref="C7">
-    <cfRule type="duplicateValues" dxfId="5" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C21:C22">
-    <cfRule type="duplicateValues" dxfId="4" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="8"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1647,7 +1703,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D63B81B-C0DE-4D5C-B8D8-1821B93262B2}">
-  <dimension ref="A1:E43"/>
+  <dimension ref="A1:E48"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="24.5703125" style="2" customWidth="1"/>
@@ -1687,6 +1743,9 @@
       <c r="D2" s="2" t="s">
         <v>31</v>
       </c>
+      <c r="E2" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="8">
@@ -1701,6 +1760,9 @@
       <c r="D3" s="2" t="s">
         <v>29</v>
       </c>
+      <c r="E3" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="4" spans="1:5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="8">
@@ -1885,6 +1947,9 @@
       <c r="D14" s="2" t="s">
         <v>43</v>
       </c>
+      <c r="E14" s="2" t="s">
+        <v>178</v>
+      </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="8">
@@ -1899,22 +1964,25 @@
       <c r="D15" s="2" t="s">
         <v>44</v>
       </c>
+      <c r="E15" s="2" t="s">
+        <v>179</v>
+      </c>
     </row>
     <row r="16" spans="1:5" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="8">
         <v>10000</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="C16" s="8" t="s">
-        <v>75</v>
+        <v>167</v>
+      </c>
+      <c r="C16" s="8">
+        <v>1</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>76</v>
+        <v>168</v>
       </c>
       <c r="E16" s="8" t="s">
-        <v>77</v>
+        <v>169</v>
       </c>
     </row>
     <row r="17" spans="1:5" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -1922,16 +1990,16 @@
         <v>10000</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="C17" s="8" t="s">
-        <v>78</v>
+        <v>167</v>
+      </c>
+      <c r="C17" s="8">
+        <v>2</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>76</v>
+        <v>170</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>77</v>
+        <v>171</v>
       </c>
     </row>
     <row r="18" spans="1:5" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -1939,16 +2007,16 @@
         <v>10000</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="C18" s="8" t="s">
-        <v>79</v>
+        <v>167</v>
+      </c>
+      <c r="C18" s="8">
+        <v>3</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>76</v>
+        <v>172</v>
       </c>
       <c r="E18" s="8" t="s">
-        <v>77</v>
+        <v>173</v>
       </c>
     </row>
     <row r="19" spans="1:5" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -1956,16 +2024,16 @@
         <v>10000</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>80</v>
-      </c>
-      <c r="C19" s="8" t="s">
-        <v>81</v>
+        <v>167</v>
+      </c>
+      <c r="C19" s="8">
+        <v>4</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>76</v>
+        <v>174</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>77</v>
+        <v>175</v>
       </c>
     </row>
     <row r="20" spans="1:5" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -1973,16 +2041,16 @@
         <v>10000</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>80</v>
-      </c>
-      <c r="C20" s="8" t="s">
-        <v>82</v>
+        <v>167</v>
+      </c>
+      <c r="C20" s="8">
+        <v>5</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>76</v>
+        <v>176</v>
       </c>
       <c r="E20" s="8" t="s">
-        <v>77</v>
+        <v>177</v>
       </c>
     </row>
     <row r="21" spans="1:5" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -1990,10 +2058,10 @@
         <v>10000</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="D21" s="8" t="s">
         <v>76</v>
@@ -2007,10 +2075,10 @@
         <v>10000</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="D22" s="8" t="s">
         <v>76</v>
@@ -2024,10 +2092,10 @@
         <v>10000</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="D23" s="8" t="s">
         <v>76</v>
@@ -2041,10 +2109,10 @@
         <v>10000</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="D24" s="8" t="s">
         <v>76</v>
@@ -2058,10 +2126,10 @@
         <v>10000</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="D25" s="8" t="s">
         <v>76</v>
@@ -2075,10 +2143,10 @@
         <v>10000</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="D26" s="8" t="s">
         <v>76</v>
@@ -2092,10 +2160,10 @@
         <v>10000</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C27" s="8" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="D27" s="8" t="s">
         <v>76</v>
@@ -2104,210 +2172,330 @@
         <v>77</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A28"/>
-      <c r="B28" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>152</v>
+    <row r="28" spans="1:5" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="8">
+        <v>10000</v>
+      </c>
+      <c r="B28" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="C28" s="8" t="s">
+        <v>86</v>
       </c>
       <c r="D28" s="8" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A29"/>
-      <c r="B29" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>153</v>
+        <v>76</v>
+      </c>
+      <c r="E28" s="8" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="8">
+        <v>10000</v>
+      </c>
+      <c r="B29" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="C29" s="8" t="s">
+        <v>87</v>
       </c>
       <c r="D29" s="8" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A30"/>
-      <c r="B30" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>154</v>
+        <v>76</v>
+      </c>
+      <c r="E29" s="8" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="8">
+        <v>10000</v>
+      </c>
+      <c r="B30" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="C30" s="8" t="s">
+        <v>89</v>
       </c>
       <c r="D30" s="8" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A31"/>
-      <c r="B31" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>155</v>
+        <v>76</v>
+      </c>
+      <c r="E30" s="8" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="8">
+        <v>10000</v>
+      </c>
+      <c r="B31" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="C31" s="8" t="s">
+        <v>90</v>
       </c>
       <c r="D31" s="8" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A32"/>
-      <c r="B32" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>156</v>
+        <v>76</v>
+      </c>
+      <c r="E31" s="8" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="8">
+        <v>10000</v>
+      </c>
+      <c r="B32" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="C32" s="8" t="s">
+        <v>91</v>
       </c>
       <c r="D32" s="8" t="s">
-        <v>146</v>
+        <v>76</v>
+      </c>
+      <c r="E32" s="8" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A33"/>
+      <c r="A33" s="11" t="s">
+        <v>166</v>
+      </c>
       <c r="B33" s="2" t="s">
         <v>141</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="D33" s="8" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A34"/>
+      <c r="A34" s="11" t="s">
+        <v>166</v>
+      </c>
       <c r="B34" s="2" t="s">
         <v>141</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="D34" s="8" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A35"/>
+      <c r="A35" s="11" t="s">
+        <v>166</v>
+      </c>
       <c r="B35" s="2" t="s">
         <v>141</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="D35" s="8" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A36"/>
+      <c r="A36" s="11" t="s">
+        <v>166</v>
+      </c>
       <c r="B36" s="2" t="s">
         <v>141</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="D36" s="8" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A37"/>
+      <c r="A37" s="11" t="s">
+        <v>166</v>
+      </c>
       <c r="B37" s="2" t="s">
         <v>141</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="D37" s="8" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A38"/>
+      <c r="A38" s="11" t="s">
+        <v>166</v>
+      </c>
       <c r="B38" s="2" t="s">
         <v>141</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>26</v>
+        <v>157</v>
       </c>
       <c r="D38" s="8" t="s">
-        <v>58</v>
+        <v>147</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A39"/>
+      <c r="A39" s="11" t="s">
+        <v>166</v>
+      </c>
       <c r="B39" s="2" t="s">
-        <v>101</v>
+        <v>141</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="D39" s="2" t="s">
-        <v>102</v>
+        <v>158</v>
+      </c>
+      <c r="D39" s="8" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A40"/>
+      <c r="A40" s="11" t="s">
+        <v>166</v>
+      </c>
       <c r="B40" s="2" t="s">
-        <v>101</v>
+        <v>141</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="D40" s="2" t="s">
-        <v>103</v>
+        <v>159</v>
+      </c>
+      <c r="D40" s="8" t="s">
+        <v>149</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A41"/>
+      <c r="A41" s="11" t="s">
+        <v>166</v>
+      </c>
       <c r="B41" s="2" t="s">
-        <v>101</v>
+        <v>141</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="D41" s="2" t="s">
-        <v>104</v>
+        <v>160</v>
+      </c>
+      <c r="D41" s="8" t="s">
+        <v>150</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A42"/>
+      <c r="A42" s="11" t="s">
+        <v>166</v>
+      </c>
       <c r="B42" s="2" t="s">
-        <v>101</v>
+        <v>141</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="D42" s="2" t="s">
-        <v>105</v>
+        <v>161</v>
+      </c>
+      <c r="D42" s="8" t="s">
+        <v>151</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A43"/>
+      <c r="A43" s="11" t="s">
+        <v>166</v>
+      </c>
       <c r="B43" s="2" t="s">
-        <v>101</v>
+        <v>141</v>
       </c>
       <c r="C43" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="D43" s="2" t="s">
+      <c r="D43" s="8" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A44" s="11" t="s">
+        <v>164</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A45" s="11" t="s">
+        <v>164</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A46" s="11" t="s">
+        <v>164</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A47" s="11" t="s">
+        <v>164</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A48" s="11" t="s">
+        <v>164</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D48" s="2" t="s">
         <v>58</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="C4:C6">
-    <cfRule type="duplicateValues" dxfId="3" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C7:C10">
+    <cfRule type="duplicateValues" dxfId="3" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C11:C12">
     <cfRule type="duplicateValues" dxfId="2" priority="2"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C11:C12">
-    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
+  <conditionalFormatting sqref="C21:C32">
+    <cfRule type="duplicateValues" dxfId="1" priority="15"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C16:C27">
-    <cfRule type="duplicateValues" dxfId="0" priority="14"/>
+  <conditionalFormatting sqref="C16:C20">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2349,26 +2537,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="d0fa6634-326e-4532-91a2-52bea7ac9212" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f4877444-78fa-4cfa-bafc-d6c64fafc061">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100DE51FB2AFBB2DD429D3D11FE759FFC43" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="1354c8e90e28409d311bbba5db8dc335">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f4877444-78fa-4cfa-bafc-d6c64fafc061" xmlns:ns3="d0fa6634-326e-4532-91a2-52bea7ac9212" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="dbb4473bd7833dc3543803a005841490" ns2:_="" ns3:_="">
     <xsd:import namespace="f4877444-78fa-4cfa-bafc-d6c64fafc061"/>
@@ -2609,26 +2777,27 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{38DBD55A-6A6F-4CFC-88B1-45940F719B9F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{08E67F88-34D7-4F06-AD9D-1E85A09096B5}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="d0fa6634-326e-4532-91a2-52bea7ac9212"/>
-    <ds:schemaRef ds:uri="f4877444-78fa-4cfa-bafc-d6c64fafc061"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="d0fa6634-326e-4532-91a2-52bea7ac9212" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f4877444-78fa-4cfa-bafc-d6c64fafc061">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EEE20FAB-4766-46A5-8028-431F2E6E2BC1}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2645,4 +2814,23 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{38DBD55A-6A6F-4CFC-88B1-45940F719B9F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{08E67F88-34D7-4F06-AD9D-1E85A09096B5}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="d0fa6634-326e-4532-91a2-52bea7ac9212"/>
+    <ds:schemaRef ds:uri="f4877444-78fa-4cfa-bafc-d6c64fafc061"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>